--- a/语音/无水调试.xlsx
+++ b/语音/无水调试.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="303">
   <si>
     <t>操作名称</t>
   </si>
@@ -125,6 +125,9 @@
     <t>全溢流值与调整值一致，不再升高</t>
   </si>
   <si>
+    <t>已反复确认三次溢流值为调整值</t>
+  </si>
+  <si>
     <t>检查1号发电机油压装置自动控制屏，油压、油位与实际值一致</t>
   </si>
   <si>
@@ -254,6 +257,9 @@
     <t>已验证机组处于静止状态，压油装置已投入，机组处于无水流状态，开始调速器电调柜上电</t>
   </si>
   <si>
+    <t>已完成接力器油管路检查</t>
+  </si>
+  <si>
     <t>打开1号水轮机调速器电调柜柜门</t>
   </si>
   <si>
@@ -272,13 +278,13 @@
     <t>已完成调速器电调柜跨接线检查</t>
   </si>
   <si>
-    <t>检查1号水轮机调速器电调柜各空气开关，交流、直流电源总开关、加热器电源开关、A套、B套PCC电源、均在分闸位置</t>
+    <t>检查1号水轮机调速器电调柜各空气开关，交流，直流电源总开关，加热器电源开关，A套，B套P.C.C电源，均在分闸位置</t>
   </si>
   <si>
     <t>检查1号水轮机调速器电调柜各空气开关</t>
   </si>
   <si>
-    <t>交流、直流电源总开关、加热器电源开关、A套、B套PCC电源、均在分闸位置</t>
+    <t>交流，直流电源总开关，加热器电源开关，A套，B套P.C.C电源，均在分闸位置</t>
   </si>
   <si>
     <t>已完成调速器电调柜空气开关检查</t>
@@ -368,10 +374,10 @@
     <t>加热器供电电源已合闸</t>
   </si>
   <si>
-    <t>A套B套PCC电源合闸</t>
-  </si>
-  <si>
-    <t>A套B套PCC电源已合闸</t>
+    <t>A套B套P.C.C电源合闸</t>
+  </si>
+  <si>
+    <t>A套B套P.C.C电源已合闸</t>
   </si>
   <si>
     <t>检查调速器电调柜显示屏，显示屏正常显示画面</t>
@@ -386,6 +392,9 @@
     <t>调速器已投入，开始残压测频和齿盘测频</t>
   </si>
   <si>
+    <t>已完成调速器电调柜显示屏检查</t>
+  </si>
+  <si>
     <t>残压测频和齿盘测频</t>
   </si>
   <si>
@@ -395,7 +404,7 @@
     <t>已放置脉冲发生器</t>
   </si>
   <si>
-    <t>使用脉冲发生器，接入电调柜端子排XT131:1端口</t>
+    <t>将脉冲发生器，测试脉冲输出线，接入电调柜端子排XT131:1端口</t>
   </si>
   <si>
     <t>已接入测试脉冲</t>
@@ -413,7 +422,7 @@
     <t>已完成A套残压测频检查</t>
   </si>
   <si>
-    <t>使用脉冲发生器，接入电调柜端子排XT131:3端口</t>
+    <t>将脉冲发生器，测试脉冲输出线，接入电调柜端子排XT131:3端口</t>
   </si>
   <si>
     <t>在调速器电调柜显示屏上观察B套残压测频是否与输入一致，B机残压测频四十八渐变到五十二赫兹，机组转速96每分钟渐变到104每分钟</t>
@@ -428,7 +437,7 @@
     <t>已完成B套残压测频检查</t>
   </si>
   <si>
-    <t>使用脉冲发生器，接入电调柜端子排XT132:5端口</t>
+    <t>将脉冲发生器，测试脉冲输出线，接入电调柜端子排XT132:5端口</t>
   </si>
   <si>
     <t>在调速器电调柜显示屏上观察B套齿盘测频是否与输入一致，B套齿盘测频0赫兹渐变到50赫兹，机组转速0每分钟渐变到100每分钟</t>
@@ -443,7 +452,7 @@
     <t>已完成B套齿盘测频</t>
   </si>
   <si>
-    <t>使用脉冲发生器，接入电调柜端子排XT132:3端口</t>
+    <t>将脉冲发生器，测试脉冲输出线，接入电调柜端子排XT132:3端口</t>
   </si>
   <si>
     <t>在调速器电调柜显示屏上观察A套齿盘测频是否与输入一致，A套齿盘测频0赫兹渐变到50赫兹，机组转速0每分钟渐变到100每分钟</t>
@@ -461,9 +470,15 @@
     <t>后续无水试验需要脉冲发生器持续输出信号，模拟机组旋转，调速器柜门不完全关闭</t>
   </si>
   <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>已验证发电机残压测频回路正常，齿盘测速传感器及回路正常，开始开度传感器标定和开关机时长测量</t>
   </si>
   <si>
+    <t>已关闭调速器柜门</t>
+  </si>
+  <si>
     <t>开度传感器标定和开关机时长测量</t>
   </si>
   <si>
@@ -530,13 +545,10 @@
     <t>使用计时器记录导叶关机全行程时间，手动给定导叶开度，从99%到0%</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>T1阶段3.7秒，导叶开度快速关闭</t>
-  </si>
-  <si>
-    <t>T2阶段 9.6秒，导叶开度缓慢关闭</t>
+    <t>T1阶段3.2秒，导叶快速关闭</t>
+  </si>
+  <si>
+    <t>T2阶段 9.8秒，导叶开度缓慢关闭</t>
   </si>
   <si>
     <t>导叶关机，用时13.3秒，与设计时间一致，无需调整导叶柜开关机螺杆</t>
@@ -575,7 +587,7 @@
     <t>发现报警：“调速器紧急停机动作”，“导叶紧急关闭”</t>
   </si>
   <si>
-    <t>已完成事故配压阀关机，用时14秒，与设计时间一致</t>
+    <t>已完成报警界面检查</t>
   </si>
   <si>
     <t>点击故障复归按钮，解除自锁，清除报警事件</t>
@@ -590,6 +602,9 @@
     <t>已完成开度传感器标定和开关机时长测量，开始双机切换试验，和模拟动作试验</t>
   </si>
   <si>
+    <t>已完成故障复归操作</t>
+  </si>
+  <si>
     <t>双机切换试验，和模拟动作试验</t>
   </si>
   <si>
@@ -644,7 +659,7 @@
     <t>进入空载状态，“冷却水流量低”报警</t>
   </si>
   <si>
-    <t>已完成调速器电调柜显示屏数据信息检查</t>
+    <t>已确认调速器收到开机令</t>
   </si>
   <si>
     <t>空载状态，从A机主用切至B机主用，导叶接力器开度保持不变</t>
@@ -674,7 +689,7 @@
     <t>进入负载运行状态，导叶开度变为额定开度79%， “功率反馈偏差越限”报警</t>
   </si>
   <si>
-    <t>已完成调速器电调柜液晶显示屏数据信息检查</t>
+    <t>已确认调速器收到断路器合令</t>
   </si>
   <si>
     <t>负载状态，从A机主用切至B机主用，导叶接力器开度保持不变</t>
@@ -683,6 +698,129 @@
     <t>负载状态，从B机主用切至A机主用，导叶接力器开度保持不变</t>
   </si>
   <si>
+    <t>检查电调柜显示屏A机操作界面，导叶接力器开度变化小于1%</t>
+  </si>
+  <si>
+    <t>检查电调柜显示屏A机操作界面</t>
+  </si>
+  <si>
+    <t>导叶接力器开度变化小于1%</t>
+  </si>
+  <si>
+    <t>检查LCUA1柜触摸屏报警界面，发现交流电源消失信号报警</t>
+  </si>
+  <si>
+    <t>检查LCUA1柜触摸屏报警界面</t>
+  </si>
+  <si>
+    <t>发现交流电源消失信号报警</t>
+  </si>
+  <si>
+    <t>已确认LCU收到交流电源消失信号</t>
+  </si>
+  <si>
+    <t>直流供电电源分闸，直流指示灯熄灭</t>
+  </si>
+  <si>
+    <t>直流供电电源分闸</t>
+  </si>
+  <si>
+    <t>直流指示灯熄灭</t>
+  </si>
+  <si>
+    <t>电调柜直流电源空开已分闸</t>
+  </si>
+  <si>
+    <t>检查LCUA1柜触摸屏报警界面，发现直流电源消失信号报警</t>
+  </si>
+  <si>
+    <t>发现直流电源消失信号报警</t>
+  </si>
+  <si>
+    <t>已确认LCU收到直流电源消失信号</t>
+  </si>
+  <si>
+    <t>检查电调柜显示屏，电调柜屏幕熄灭</t>
+  </si>
+  <si>
+    <t>检查电调柜显示屏</t>
+  </si>
+  <si>
+    <t>电调柜屏幕熄灭</t>
+  </si>
+  <si>
+    <t>已完成电调柜显示屏检查</t>
+  </si>
+  <si>
+    <t>检查电调柜显示屏A机操作界面，A套控制状态不变，导叶接力器开度变化小于1%</t>
+  </si>
+  <si>
+    <t>A套控制状态不变，导叶接力器开度变化小于1%</t>
+  </si>
+  <si>
+    <t>关闭1号水轮机调速器电调柜内柜门</t>
+  </si>
+  <si>
+    <t>调速器电调柜内柜门不完全关闭</t>
+  </si>
+  <si>
+    <t>记录当前调速器电调柜触摸屏导叶开度值，等待半小时后，观察开度漂移量</t>
+  </si>
+  <si>
+    <t>记录当前调速器电调柜导叶开度值</t>
+  </si>
+  <si>
+    <t>记录开度值后，假设调速器已处于负载状态运行了半小时</t>
+  </si>
+  <si>
+    <t>已记录当前调速器电调柜导叶开度值</t>
+  </si>
+  <si>
+    <t>检查电调柜显示屏A机操作界面，导叶接力器开度变化小于1%，漂移量小于1%</t>
+  </si>
+  <si>
+    <t>导叶接力器开度变化小于1%，漂移量小于1%</t>
+  </si>
+  <si>
+    <t>已完成导叶开度的漂移量检查</t>
+  </si>
+  <si>
+    <t>在LCUA1柜控制界面，发出断路器分令</t>
+  </si>
+  <si>
+    <t>已发送断路器分令</t>
+  </si>
+  <si>
+    <t>检查调速器电调柜事件报告界面，接收到断路器分信号，空载状态，导叶开度变为预设空载开度</t>
+  </si>
+  <si>
+    <t>检查调速器电调柜事件报告界面，接收到断路器分信号</t>
+  </si>
+  <si>
+    <t>空载状态，导叶开度变为预设空载开度</t>
+  </si>
+  <si>
+    <t>已确认调速器收到断路器分令</t>
+  </si>
+  <si>
+    <t>在LCUA1柜控制界面，发出停机令</t>
+  </si>
+  <si>
+    <t>已发送停机令</t>
+  </si>
+  <si>
+    <t>检查调速器电调柜事件报告界面，接收到停机令，切换到停机备用状态，导叶开度全关</t>
+  </si>
+  <si>
+    <t>检查调速器电调柜事件报告界面，接收到停机令</t>
+  </si>
+  <si>
+    <t>切换到停机备用状态，导叶开度全关</t>
+  </si>
+  <si>
+    <t>已确认调速器收到停机令</t>
+  </si>
+  <si>
     <t>点击调速器电调柜显示屏A机操作界面的“不跟踪”，跟踪模式显示“跟踪频给”</t>
   </si>
   <si>
@@ -692,148 +830,34 @@
     <t>跟踪模式显示“跟踪频给”</t>
   </si>
   <si>
-    <t>已完成跟踪模式切换</t>
-  </si>
-  <si>
-    <t>点击调速器电调柜显示屏A机操作界面的“跟踪”，，跟踪模式显示“跟踪网频”</t>
-  </si>
-  <si>
-    <t>点击调速器电调柜显示屏A机操作界面的“跟踪”，</t>
+    <t>调速器跟踪模式已切换到跟踪频给</t>
+  </si>
+  <si>
+    <t>点击调速器电调柜显示屏A机操作界面的“跟踪”，跟踪模式显示“跟踪网频”</t>
+  </si>
+  <si>
+    <t>点击调速器电调柜显示屏A机操作界面的“跟踪”</t>
   </si>
   <si>
     <t>跟踪模式显示“跟踪网频”</t>
   </si>
   <si>
-    <t>检查电调柜显示屏A机操作界面，导叶接力器开度变化小于1%</t>
-  </si>
-  <si>
-    <t>检查电调柜显示屏A机操作界面</t>
-  </si>
-  <si>
-    <t>导叶接力器开度变化小于1%</t>
-  </si>
-  <si>
-    <t>检查LCUA1柜触摸屏报警界面，发现交流电源消失信号报警</t>
-  </si>
-  <si>
-    <t>检查LCUA1柜触摸屏报警界面</t>
-  </si>
-  <si>
-    <t>发现交流电源消失信号报警</t>
-  </si>
-  <si>
-    <t>已确认LCU收到交流电源消失信号</t>
-  </si>
-  <si>
-    <t>直流供电电源分闸，直流指示灯熄灭</t>
-  </si>
-  <si>
-    <t>直流供电电源分闸</t>
-  </si>
-  <si>
-    <t>直流指示灯熄灭</t>
-  </si>
-  <si>
-    <t>电调柜直流电源空开已分闸</t>
-  </si>
-  <si>
-    <t>检查LCUA1柜触摸屏报警界面，发现直流电源消失信号报警</t>
-  </si>
-  <si>
-    <t>发现直流电源消失信号报警</t>
-  </si>
-  <si>
-    <t>已确认LCU收到直流电源消失信号</t>
-  </si>
-  <si>
-    <t>检查电调柜显示屏，电调柜屏幕熄灭</t>
-  </si>
-  <si>
-    <t>检查电调柜显示屏</t>
-  </si>
-  <si>
-    <t>电调柜屏幕熄灭</t>
-  </si>
-  <si>
-    <t>已完成电调柜显示屏检查</t>
-  </si>
-  <si>
-    <t>检查电调柜显示屏A机操作界面，A套控制状态不变，导叶接力器开度变化小于1%</t>
-  </si>
-  <si>
-    <t>A套控制状态不变，导叶接力器开度变化小于1%</t>
-  </si>
-  <si>
-    <t>关闭1号水轮机调速器电调柜内柜门</t>
-  </si>
-  <si>
-    <t>调速器电调柜内柜门不完全关闭</t>
-  </si>
-  <si>
-    <t>记录当前调速器电调柜导叶开度值，等待半小时后，观察开度漂移量</t>
-  </si>
-  <si>
-    <t>记录当前调速器电调柜导叶开度值</t>
-  </si>
-  <si>
-    <t>等待半小时后，观察开度漂移量</t>
-  </si>
-  <si>
-    <t>已记录当前调速器电调柜导叶开度值</t>
-  </si>
-  <si>
-    <t>检查电调柜显示屏A机操作界面，导叶接力器开度变化小于1%，漂移量小于1%</t>
-  </si>
-  <si>
-    <t>导叶接力器开度变化小于1%，漂移量小于1%</t>
-  </si>
-  <si>
-    <t>已完成导叶开度的漂移量检查</t>
-  </si>
-  <si>
-    <t>在LCUA1柜控制界面，发出断路器分令</t>
-  </si>
-  <si>
-    <t>已发送断路器分令</t>
-  </si>
-  <si>
-    <t>检查调速器电调柜事件报告界面，接收到断路器分信号，空载状态，导叶开度变为预设最小空载开度9%</t>
-  </si>
-  <si>
-    <t>检查调速器电调柜事件报告界面，接收到断路器分信号</t>
-  </si>
-  <si>
-    <t>空载状态，导叶开度变为预设最小空载开度9%</t>
-  </si>
-  <si>
-    <t>在LCUA1柜控制界面，发出停机令</t>
-  </si>
-  <si>
-    <t>已发送停机令</t>
-  </si>
-  <si>
-    <t>检查调速器电调柜事件报告界面，接收到停机令，切换到停机备用状态，导叶开度全关</t>
-  </si>
-  <si>
-    <t>检查调速器电调柜事件报告界面，接收到停机令</t>
-  </si>
-  <si>
-    <t>切换到停机备用状态，导叶开度全关</t>
-  </si>
-  <si>
     <t>已完成空载，负载状态下双机切换试验，和模拟动作试验，开始静特性试验</t>
   </si>
   <si>
+    <t>调速器跟踪模式已切换到跟踪网频</t>
+  </si>
+  <si>
     <t>静特性试验</t>
   </si>
   <si>
-    <t>点击调速器电调柜触摸屏静特性试验界面，设置P-I-D参数，点击开始按钮，对A机进行静特性试验</t>
+    <t>点击调速器电调柜触摸屏静特性试验界面，设置P.I.D参数，点击开始按钮，对A机进行静特性试验</t>
   </si>
   <si>
     <t>已切换到跟踪频给状态</t>
   </si>
   <si>
-    <t>P.I.D参数已设置： KP=9.99%, KI=9.99%, KD=0秒，BP=6%，电气开限=99.99%，</t>
+    <t>P.I.D参数已设置： Kp=9.99%, Kd=0秒，Ki=9.99%, bp=6%，电气开限=99.99%</t>
   </si>
   <si>
     <t>正在绘制开方向桨叶开度，对应频率从50赫兹变化到52赫兹</t>
@@ -845,7 +869,7 @@
     <t>试验最大转速死区小于0.012%，试验结论：合格</t>
   </si>
   <si>
-    <t>已完成A机静特性试验</t>
+    <t>已完成A机无水调试静特性试验</t>
   </si>
   <si>
     <t>查看A机静特性试验结果报告</t>
@@ -866,9 +890,6 @@
     <t>点击调速器电调柜触摸屏静特性试验界面，点击开始按钮，对B机进行静特性试验</t>
   </si>
   <si>
-    <t>PID参数已设置： KP=9.99%, KI=9.99%, KD=0秒，BP=6%，电气开限=99.99%，</t>
-  </si>
-  <si>
     <t>正在绘制开方向桨叶开度，对应频率从50赫兹,变化到52赫兹</t>
   </si>
   <si>
@@ -878,7 +899,7 @@
     <t>试验最大转速死区小于0.011%，试验结论：合格</t>
   </si>
   <si>
-    <t>已完成B机静特性试验</t>
+    <t>已完成B机无水调试静特性试验</t>
   </si>
   <si>
     <t>查看B机静特性试验结果报告</t>
@@ -909,6 +930,9 @@
   </si>
   <si>
     <t>关闭LCUA1柜柜门</t>
+  </si>
+  <si>
+    <t>已关闭LCUA1柜柜门</t>
   </si>
   <si>
     <t>已完成1号水轮机调速器无水调试</t>
@@ -1545,7 +1569,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1555,6 +1579,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1939,7 +1966,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J288"/>
+  <dimension ref="A1:J297"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="34.5083333333333" customWidth="1"/>
@@ -2232,7 +2259,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>12</v>
@@ -2244,10 +2271,10 @@
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>1</v>
@@ -2260,7 +2287,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>8</v>
@@ -2273,7 +2300,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>12</v>
@@ -2285,10 +2312,10 @@
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>1</v>
@@ -2301,7 +2328,7 @@
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -2313,10 +2340,10 @@
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>1</v>
@@ -2329,7 +2356,7 @@
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
@@ -2342,7 +2369,7 @@
       <c r="B29" s="2"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -2354,10 +2381,10 @@
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>1</v>
@@ -2370,7 +2397,7 @@
       <c r="B31" s="2"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -2382,10 +2409,10 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>1</v>
@@ -2398,7 +2425,7 @@
       <c r="B33" s="2"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>8</v>
@@ -2411,7 +2438,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -2423,10 +2450,10 @@
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>1</v>
@@ -2439,7 +2466,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>8</v>
@@ -2452,7 +2479,7 @@
       <c r="B37" s="2"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -2464,10 +2491,10 @@
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>1</v>
@@ -2480,7 +2507,7 @@
       <c r="B39" s="2"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>8</v>
@@ -2493,7 +2520,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -2505,10 +2532,10 @@
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>1</v>
@@ -2521,7 +2548,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -2533,10 +2560,10 @@
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>1</v>
@@ -2549,7 +2576,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>8</v>
@@ -2562,7 +2589,7 @@
       <c r="B45" s="2"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
@@ -2574,10 +2601,10 @@
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>1</v>
@@ -2590,7 +2617,7 @@
       <c r="B47" s="2"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>8</v>
@@ -2603,7 +2630,7 @@
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>12</v>
@@ -2615,10 +2642,10 @@
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>1</v>
@@ -2631,7 +2658,7 @@
       <c r="B50" s="2"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>12</v>
@@ -2643,10 +2670,10 @@
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>1</v>
@@ -2659,7 +2686,7 @@
       <c r="B52" s="2"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>8</v>
@@ -2672,7 +2699,7 @@
       <c r="B53" s="2"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
@@ -2684,10 +2711,10 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>1</v>
@@ -2700,640 +2727,630 @@
       <c r="B55" s="2"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" ht="47" customHeight="1" spans="1:5">
-      <c r="A56">
-        <v>57</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" ht="30.5" customHeight="1" spans="1:5">
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" ht="30.5" customHeight="1" spans="1:5">
+        <v>75</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" ht="47" customHeight="1" spans="1:5">
       <c r="A57">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" s="2"/>
-      <c r="C57" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>75</v>
+      <c r="C57" s="3"/>
+      <c r="D57" t="s">
+        <v>76</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" ht="30.5" customHeight="1" spans="1:5">
       <c r="A58">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2"/>
-      <c r="C58" s="3"/>
+      <c r="C58" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D58" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" ht="30.5" customHeight="1" spans="1:5">
       <c r="A59">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" ht="30.5" customHeight="1" spans="1:5">
       <c r="A60">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" s="2"/>
-      <c r="C60" s="3"/>
+      <c r="C60" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D60" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" ht="30.5" customHeight="1" spans="1:5">
       <c r="A61">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2"/>
-      <c r="C61" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" ht="30.5" customHeight="1" spans="1:5">
       <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A63">
         <v>63</v>
       </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" ht="47" customHeight="1" spans="1:5">
-      <c r="A63">
-        <v>64</v>
-      </c>
       <c r="B63" s="2"/>
-      <c r="C63" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="C63" s="3"/>
       <c r="D63" s="3" t="s">
         <v>82</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" ht="47" customHeight="1" spans="1:5">
       <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" ht="47" customHeight="1" spans="1:5">
+      <c r="A65">
         <v>65</v>
-      </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A65">
-        <v>66</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" ht="30.5" customHeight="1" spans="1:5">
       <c r="A66">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2"/>
-      <c r="C66" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
         <v>86</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" ht="47" customHeight="1" spans="1:5">
       <c r="A67">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" s="2"/>
-      <c r="C67" s="3"/>
+      <c r="C67" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="D67" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" ht="30.5" customHeight="1" spans="1:5">
       <c r="A68">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" ht="30.5" customHeight="1" spans="1:5">
       <c r="A69">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" s="2"/>
-      <c r="C69" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
         <v>90</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" ht="47" customHeight="1" spans="1:5">
       <c r="A70">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" s="2"/>
-      <c r="C70" s="3"/>
+      <c r="C70" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="D70" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" ht="30.5" customHeight="1" spans="1:5">
       <c r="A71">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" ht="30.5" customHeight="1" spans="1:5">
       <c r="A72">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B72" s="2"/>
-      <c r="C72" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" ht="47" customHeight="1" spans="1:5">
       <c r="A73">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B73" s="2"/>
-      <c r="C73" s="3"/>
+      <c r="C73" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="D73" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" ht="30.5" customHeight="1" spans="1:5">
       <c r="A74">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" ht="30.5" customHeight="1" spans="1:5">
       <c r="A75">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" s="2"/>
-      <c r="C75" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" ht="30.5" customHeight="1" spans="1:5">
       <c r="A76">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" s="2"/>
-      <c r="C76" s="3"/>
+      <c r="C76" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="D76" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" ht="30.5" customHeight="1" spans="1:5">
       <c r="A77">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" ht="30.5" customHeight="1" spans="1:5">
       <c r="A78">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B78" s="2"/>
-      <c r="C78" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="C78" s="3"/>
       <c r="D78" s="3" t="s">
         <v>100</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" ht="30.5" customHeight="1" spans="1:5">
       <c r="A79">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B79" s="2"/>
-      <c r="C79" s="3"/>
+      <c r="C79" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="D79" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" ht="30.5" customHeight="1" spans="1:5">
       <c r="A80">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" ht="30.5" customHeight="1" spans="1:5">
       <c r="A81">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" s="2"/>
-      <c r="C81" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="C81" s="3"/>
       <c r="D81" s="3" t="s">
         <v>104</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" ht="30.5" customHeight="1" spans="1:5">
       <c r="A82">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B82" s="2"/>
-      <c r="C82" s="3"/>
+      <c r="C82" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="D82" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" ht="30.5" customHeight="1" spans="1:5">
       <c r="A83">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" ht="30.5" customHeight="1" spans="1:5">
       <c r="A84">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B84" s="2"/>
-      <c r="C84" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="C84" s="3"/>
       <c r="D84" s="3" t="s">
         <v>108</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" ht="30.5" customHeight="1" spans="1:5">
       <c r="A85">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" s="2"/>
-      <c r="C85" s="3"/>
+      <c r="C85" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="D85" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" ht="30.5" customHeight="1" spans="1:5">
       <c r="A86">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" ht="30.5" customHeight="1" spans="1:5">
       <c r="A87">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" s="2"/>
-      <c r="C87" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="C87" s="3"/>
       <c r="D87" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" ht="30.5" customHeight="1" spans="1:5">
       <c r="A88">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" s="2"/>
-      <c r="C88" s="3"/>
+      <c r="C88" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="D88" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" ht="30.5" customHeight="1" spans="1:5">
       <c r="A89">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" ht="30.5" customHeight="1" spans="1:5">
       <c r="A90">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B90" s="2"/>
-      <c r="C90" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="C90" s="3"/>
       <c r="D90" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" ht="30.5" customHeight="1" spans="1:5">
       <c r="A91">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91" s="2"/>
-      <c r="C91" s="3"/>
+      <c r="C91" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="D91" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" ht="30.5" customHeight="1" spans="1:5">
       <c r="A92">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" ht="30.5" customHeight="1" spans="1:5">
       <c r="A93">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B93" s="2"/>
-      <c r="C93" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="C93" s="3"/>
       <c r="D93" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" ht="30.5" customHeight="1" spans="1:5">
       <c r="A94">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B94" s="2"/>
-      <c r="C94" s="3"/>
+      <c r="C94" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="D94" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" ht="30.5" customHeight="1" spans="1:5">
       <c r="A95">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" s="2"/>
-      <c r="C95" s="3" t="s">
-        <v>113</v>
-      </c>
+      <c r="C95" s="3"/>
       <c r="D95" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" ht="30.5" customHeight="1" spans="1:5">
       <c r="A96">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B96" s="2"/>
-      <c r="C96" s="3"/>
+      <c r="C96" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="D96" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" ht="30.5" customHeight="1" spans="1:5">
       <c r="A97">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B97" s="2"/>
-      <c r="C97" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="C97" s="3"/>
       <c r="D97" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" ht="30.5" customHeight="1" spans="1:5">
       <c r="A98">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B98" s="2"/>
-      <c r="C98" s="3"/>
+      <c r="C98" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="D98" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" ht="30.5" customHeight="1" spans="1:5">
       <c r="A99">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A100">
-        <v>101</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" s="3"/>
       <c r="D100" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" ht="30.5" customHeight="1" spans="1:5">
       <c r="A101">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="3" t="s">
+      <c r="D101" t="s">
         <v>121</v>
       </c>
       <c r="E101" s="2" t="s">
@@ -3342,14 +3359,16 @@
     </row>
     <row r="102" ht="30.5" customHeight="1" spans="1:5">
       <c r="A102">
-        <v>103</v>
-      </c>
-      <c r="B102" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="C102" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>1</v>
@@ -3357,24 +3376,24 @@
     </row>
     <row r="103" ht="30.5" customHeight="1" spans="1:5">
       <c r="A103">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="104" ht="63.5" customHeight="1" spans="1:5">
+    <row r="104" ht="30.5" customHeight="1" spans="1:5">
       <c r="A104">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>125</v>
@@ -3383,9 +3402,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" ht="47" customHeight="1" spans="1:5">
+    <row r="105" ht="30.5" customHeight="1" spans="1:5">
       <c r="A105">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="3"/>
@@ -3393,264 +3412,262 @@
         <v>126</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" ht="63.5" customHeight="1" spans="1:5">
       <c r="A106">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B106" s="2"/>
-      <c r="C106" s="3"/>
+      <c r="C106" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="D106" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" ht="47" customHeight="1" spans="1:5">
       <c r="A107">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B107" s="2"/>
-      <c r="C107" s="3" t="s">
-        <v>128</v>
-      </c>
+      <c r="C107" s="3"/>
       <c r="D107" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" ht="30.5" customHeight="1" spans="1:5">
       <c r="A108">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="109" ht="63.5" customHeight="1" spans="1:5">
+    <row r="109" ht="30.5" customHeight="1" spans="1:5">
       <c r="A109">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="110" ht="47" customHeight="1" spans="1:5">
+    <row r="110" ht="30.5" customHeight="1" spans="1:5">
       <c r="A110">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" ht="63.5" customHeight="1" spans="1:5">
       <c r="A111">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2"/>
-      <c r="C111" s="3"/>
+      <c r="C111" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="D111" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" ht="47" customHeight="1" spans="1:5">
       <c r="A112">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2"/>
-      <c r="C112" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="C112" s="3"/>
       <c r="D112" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" ht="30.5" customHeight="1" spans="1:5">
       <c r="A113">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="114" ht="63.5" customHeight="1" spans="1:5">
+    <row r="114" ht="30.5" customHeight="1" spans="1:5">
       <c r="A114">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="115" ht="47" customHeight="1" spans="1:5">
+    <row r="115" ht="30.5" customHeight="1" spans="1:5">
       <c r="A115">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" ht="63.5" customHeight="1" spans="1:5">
       <c r="A116">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B116" s="2"/>
-      <c r="C116" s="3"/>
+      <c r="C116" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="D116" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" ht="47" customHeight="1" spans="1:5">
       <c r="A117">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B117" s="2"/>
-      <c r="C117" s="3" t="s">
-        <v>138</v>
-      </c>
+      <c r="C117" s="3"/>
       <c r="D117" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" ht="30.5" customHeight="1" spans="1:5">
       <c r="A118">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="119" ht="63.5" customHeight="1" spans="1:5">
+    <row r="119" ht="30.5" customHeight="1" spans="1:5">
       <c r="A119">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="120" ht="47" customHeight="1" spans="1:5">
+    <row r="120" ht="30.5" customHeight="1" spans="1:5">
       <c r="A120">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" ht="63.5" customHeight="1" spans="1:5">
       <c r="A121">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B121" s="2"/>
-      <c r="C121" s="3"/>
+      <c r="C121" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="D121" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" ht="47" customHeight="1" spans="1:5">
       <c r="A122">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B122" s="2"/>
-      <c r="C122" s="3" t="s">
-        <v>143</v>
-      </c>
+      <c r="C122" s="3"/>
       <c r="D122" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" ht="30.5" customHeight="1" spans="1:5">
       <c r="A123">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B123" s="2"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="124" ht="30.5" customHeight="1" spans="1:5">
+    <row r="124" ht="47" customHeight="1" spans="1:5">
       <c r="A124">
-        <v>125</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>145</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="B124" s="2"/>
       <c r="C124" s="3" t="s">
         <v>146</v>
       </c>
@@ -3661,37 +3678,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A125">
-        <v>126</v>
-      </c>
+    <row r="125" ht="47" customHeight="1" spans="1:5">
       <c r="B125" s="2"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A126">
-        <v>127</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" ht="47" customHeight="1" spans="1:5">
       <c r="B126" s="2"/>
-      <c r="C126" s="3" t="s">
-        <v>148</v>
-      </c>
+      <c r="C126" s="3"/>
       <c r="D126" s="3" t="s">
         <v>148</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" ht="30.5" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" ht="47" customHeight="1" spans="1:5">
       <c r="A127">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B127" s="2"/>
       <c r="C127" s="3"/>
@@ -3702,13 +3711,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" ht="47" customHeight="1" spans="1:5">
+    <row r="128" ht="30.5" customHeight="1" spans="1:5">
       <c r="A128">
-        <v>129</v>
-      </c>
-      <c r="B128" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="C128" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>151</v>
@@ -3719,7 +3730,7 @@
     </row>
     <row r="129" ht="30.5" customHeight="1" spans="1:5">
       <c r="A129">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B129" s="2"/>
       <c r="C129" s="3"/>
@@ -3727,53 +3738,55 @@
         <v>152</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" ht="30.5" customHeight="1" spans="1:5">
       <c r="A130">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B130" s="2"/>
-      <c r="C130" s="3"/>
+      <c r="C130" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="D130" s="3" t="s">
         <v>153</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" ht="63.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" ht="30.5" customHeight="1" spans="1:5">
       <c r="A131">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B131" s="2"/>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="3"/>
+      <c r="D131" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="E131" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" ht="47" customHeight="1" spans="1:5">
       <c r="A132">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B132" s="2"/>
-      <c r="C132" s="3"/>
+      <c r="C132" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="D132" s="3" t="s">
         <v>156</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" ht="30.5" customHeight="1" spans="1:5">
       <c r="A133">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3"/>
@@ -3781,40 +3794,40 @@
         <v>157</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" ht="30.5" customHeight="1" spans="1:5">
       <c r="A134">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B134" s="2"/>
-      <c r="C134" s="3" t="s">
+      <c r="C134" s="3"/>
+      <c r="D134" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D134" s="3" t="s">
+      <c r="E134" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" ht="63.5" customHeight="1" spans="1:5">
+      <c r="A135">
+        <v>132</v>
+      </c>
+      <c r="B135" s="2"/>
+      <c r="C135" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A135">
-        <v>136</v>
-      </c>
-      <c r="B135" s="2"/>
-      <c r="C135" s="3"/>
       <c r="D135" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" ht="47" customHeight="1" spans="1:5">
       <c r="A136">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B136" s="2"/>
       <c r="C136" s="3"/>
@@ -3822,40 +3835,40 @@
         <v>161</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="137" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" ht="30.5" customHeight="1" spans="1:5">
       <c r="A137">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B137" s="2"/>
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="3"/>
+      <c r="D137" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="E137" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" ht="30.5" customHeight="1" spans="1:5">
       <c r="A138">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B138" s="2"/>
-      <c r="C138" s="3"/>
+      <c r="C138" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="D138" s="3" t="s">
         <v>164</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" ht="30.5" customHeight="1" spans="1:5">
       <c r="A139">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B139" s="2"/>
       <c r="C139" s="3"/>
@@ -3863,45 +3876,45 @@
         <v>165</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" ht="30.5" customHeight="1" spans="1:5">
       <c r="A140">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B140" s="2"/>
-      <c r="C140" s="3" t="s">
-        <v>166</v>
-      </c>
+      <c r="C140" s="3"/>
       <c r="D140" s="3" t="s">
         <v>166</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" ht="47" customHeight="1" spans="1:5">
       <c r="A141">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B141" s="2"/>
-      <c r="C141" s="3"/>
+      <c r="C141" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="D141" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" ht="30.5" customHeight="1" spans="1:5">
       <c r="A142">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B142" s="2"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>8</v>
@@ -3909,53 +3922,53 @@
     </row>
     <row r="143" ht="30.5" customHeight="1" spans="1:5">
       <c r="A143">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" ht="47" customHeight="1" spans="1:5">
       <c r="A144">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B144" s="2"/>
-      <c r="C144" s="3"/>
+      <c r="C144" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="D144" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" ht="30.5" customHeight="1" spans="1:5">
       <c r="A145">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B145" s="2"/>
-      <c r="C145" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="C145" s="3"/>
       <c r="D145" s="3" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" ht="30.5" customHeight="1" spans="1:5">
       <c r="A146">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B146" s="2"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>8</v>
@@ -3963,66 +3976,66 @@
     </row>
     <row r="147" ht="30.5" customHeight="1" spans="1:5">
       <c r="A147">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="148" ht="30.5" customHeight="1" spans="1:5">
+    <row r="148" ht="47" customHeight="1" spans="1:5">
       <c r="A148">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" ht="47" customHeight="1" spans="1:5">
       <c r="A149">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B149" s="2"/>
-      <c r="C149" s="3"/>
+      <c r="C149" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="D149" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" ht="30.5" customHeight="1" spans="1:5">
       <c r="A150">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B150" s="2"/>
-      <c r="C150" s="3" t="s">
-        <v>175</v>
-      </c>
+      <c r="C150" s="3"/>
       <c r="D150" s="3" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" ht="30.5" customHeight="1" spans="1:5">
       <c r="A151">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>8</v>
@@ -4030,63 +4043,66 @@
     </row>
     <row r="152" ht="30.5" customHeight="1" spans="1:5">
       <c r="A152">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B152" s="2"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="153" ht="30.5" customHeight="1" spans="1:5">
+    <row r="153" ht="47" customHeight="1" spans="1:5">
       <c r="A153">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" ht="47" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" ht="30.5" customHeight="1" spans="1:5">
       <c r="A154">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B154" s="2"/>
-      <c r="C154" s="3"/>
+      <c r="C154" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="D154" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" ht="30.5" customHeight="1" spans="1:5">
       <c r="A155">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B155" s="2"/>
-      <c r="C155" s="3" t="s">
-        <v>179</v>
-      </c>
+      <c r="C155" s="3"/>
       <c r="D155" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A156">
+        <v>153</v>
+      </c>
       <c r="B156" s="2"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>8</v>
@@ -4094,7 +4110,7 @@
     </row>
     <row r="157" ht="30.5" customHeight="1" spans="1:5">
       <c r="A157">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B157" s="2"/>
       <c r="C157" s="3"/>
@@ -4105,9 +4121,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" ht="30.5" customHeight="1" spans="1:5">
+    <row r="158" ht="47" customHeight="1" spans="1:5">
       <c r="A158">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B158" s="2"/>
       <c r="C158" s="3"/>
@@ -4118,9 +4134,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" ht="30.5" customHeight="1" spans="1:5">
+    <row r="159" ht="47" customHeight="1" spans="1:5">
       <c r="A159">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B159" s="2"/>
       <c r="C159" s="3" t="s">
@@ -4133,113 +4149,105 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A160">
-        <v>160</v>
-      </c>
+    <row r="160" ht="47" customHeight="1" spans="1:5">
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="161" ht="47" customHeight="1" spans="1:5">
+    <row r="161" ht="30.5" customHeight="1" spans="1:5">
       <c r="A161">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B161" s="2"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" ht="30.5" customHeight="1" spans="1:5">
       <c r="A162">
-        <v>162</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>188</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B162" s="2"/>
+      <c r="C162" s="3"/>
       <c r="D162" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" ht="30.5" customHeight="1" spans="1:5">
       <c r="A163">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B163" s="2"/>
-      <c r="C163" s="3"/>
+      <c r="C163" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="D163" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" ht="30.5" customHeight="1" spans="1:5">
       <c r="A164">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B164" s="2"/>
-      <c r="C164" s="3" t="s">
-        <v>190</v>
-      </c>
+      <c r="C164" s="3"/>
       <c r="D164" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" ht="30.5" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" ht="47" customHeight="1" spans="1:5">
       <c r="A165">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B165" s="2"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="166" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A166">
-        <v>166</v>
-      </c>
       <c r="B166" s="2"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A167">
+        <v>162</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E166" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="167" ht="47" customHeight="1" spans="1:5">
-      <c r="A167">
-        <v>167</v>
-      </c>
-      <c r="B167" s="2"/>
-      <c r="C167" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="D167" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>1</v>
@@ -4247,65 +4255,65 @@
     </row>
     <row r="168" ht="30.5" customHeight="1" spans="1:5">
       <c r="A168">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B168" s="2"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169" ht="30.5" customHeight="1" spans="1:5">
       <c r="A169">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B169" s="2"/>
-      <c r="C169" s="3"/>
+      <c r="C169" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="D169" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" ht="30.5" customHeight="1" spans="1:5">
       <c r="A170">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B170" s="2"/>
-      <c r="C170" s="3" t="s">
-        <v>198</v>
-      </c>
+      <c r="C170" s="3"/>
       <c r="D170" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" ht="30.5" customHeight="1" spans="1:5">
       <c r="A171">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B171" s="2"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="172" ht="30.5" customHeight="1" spans="1:5">
+    <row r="172" ht="47" customHeight="1" spans="1:5">
       <c r="A172">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B172" s="2"/>
       <c r="C172" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>200</v>
@@ -4316,7 +4324,7 @@
     </row>
     <row r="173" ht="30.5" customHeight="1" spans="1:5">
       <c r="A173">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B173" s="2"/>
       <c r="C173" s="3"/>
@@ -4324,60 +4332,60 @@
         <v>201</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="174" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" ht="30.5" customHeight="1" spans="1:5">
       <c r="A174">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B174" s="2"/>
-      <c r="C174" s="3" t="s">
+      <c r="C174" s="3"/>
+      <c r="D174" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="E174" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" ht="30.5" customHeight="1" spans="1:5">
       <c r="A175">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B175" s="2"/>
-      <c r="C175" s="3"/>
+      <c r="C175" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="D175" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" ht="30.5" customHeight="1" spans="1:5">
       <c r="A176">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B176" s="2"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="177" ht="47" customHeight="1" spans="1:5">
+    <row r="177" ht="30.5" customHeight="1" spans="1:5">
       <c r="A177">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B177" s="2"/>
       <c r="C177" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>1</v>
@@ -4385,12 +4393,12 @@
     </row>
     <row r="178" ht="30.5" customHeight="1" spans="1:5">
       <c r="A178">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B178" s="2"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>12</v>
@@ -4398,11 +4406,11 @@
     </row>
     <row r="179" ht="47" customHeight="1" spans="1:5">
       <c r="A179">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B179" s="2"/>
       <c r="C179" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>208</v>
@@ -4413,7 +4421,7 @@
     </row>
     <row r="180" ht="30.5" customHeight="1" spans="1:5">
       <c r="A180">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B180" s="2"/>
       <c r="C180" s="3"/>
@@ -4421,88 +4429,88 @@
         <v>209</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181" ht="30.5" customHeight="1" spans="1:5">
       <c r="A181">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B181" s="2"/>
-      <c r="C181" s="3" t="s">
-        <v>210</v>
-      </c>
+      <c r="C181" s="3"/>
       <c r="D181" s="3" t="s">
         <v>210</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" ht="47" customHeight="1" spans="1:5">
       <c r="A182">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B182" s="2"/>
-      <c r="C182" s="3"/>
+      <c r="C182" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D182" s="3" t="s">
         <v>211</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="183" ht="63.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" ht="30.5" customHeight="1" spans="1:5">
       <c r="A183">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B183" s="2"/>
-      <c r="C183" s="3" t="s">
+      <c r="C183" s="3"/>
+      <c r="D183" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="E183" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184" ht="47" customHeight="1" spans="1:5">
       <c r="A184">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B184" s="2"/>
-      <c r="C184" s="3"/>
+      <c r="C184" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="D184" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" ht="30.5" customHeight="1" spans="1:5">
       <c r="A185">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B185" s="2"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="186" ht="47" customHeight="1" spans="1:5">
+    <row r="186" ht="30.5" customHeight="1" spans="1:5">
       <c r="A186">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B186" s="2"/>
       <c r="C186" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>1</v>
@@ -4510,726 +4518,723 @@
     </row>
     <row r="187" ht="30.5" customHeight="1" spans="1:5">
       <c r="A187">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="188" ht="47" customHeight="1" spans="1:5">
+    <row r="188" ht="63.5" customHeight="1" spans="1:5">
       <c r="A188">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B188" s="2"/>
       <c r="C188" s="3" t="s">
         <v>217</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="189" ht="30.5" customHeight="1" spans="1:5">
+    <row r="189" ht="47" customHeight="1" spans="1:5">
       <c r="A189">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B189" s="2"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" ht="30.5" customHeight="1" spans="1:5">
       <c r="A190">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B190" s="2"/>
-      <c r="C190" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="C190" s="3"/>
       <c r="D190" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" ht="47" customHeight="1" spans="1:5">
       <c r="A191">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B191" s="2"/>
-      <c r="C191" s="3"/>
+      <c r="C191" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="D191" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" ht="30.5" customHeight="1" spans="1:5">
       <c r="A192">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="193" ht="47" customHeight="1" spans="1:5">
+    <row r="193" ht="47" customHeight="1" spans="1:7">
       <c r="A193">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" s="3" t="s">
         <v>222</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="194" ht="30.5" customHeight="1" spans="1:5">
+    <row r="194" ht="30.5" customHeight="1" spans="1:7">
       <c r="A194">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="195" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" ht="47" customHeight="1" spans="1:7">
       <c r="A195">
-        <v>195</v>
-      </c>
-      <c r="B195" s="2"/>
-      <c r="C195" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D195" s="3" t="s">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="196" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2"/>
+    </row>
+    <row r="196" ht="30.5" customHeight="1" spans="1:7">
       <c r="A196">
-        <v>196</v>
-      </c>
-      <c r="B196" s="2"/>
-      <c r="C196" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C196" s="3"/>
       <c r="D196" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="G196" s="2"/>
+    </row>
+    <row r="197" ht="30.5" customHeight="1" spans="1:7">
       <c r="A197">
-        <v>197</v>
-      </c>
-      <c r="B197" s="2"/>
-      <c r="C197" s="3"/>
+        <v>192</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="D197" s="3" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="198" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="G197" s="2"/>
+    </row>
+    <row r="198" ht="47" customHeight="1" spans="1:7">
       <c r="A198">
-        <v>198</v>
-      </c>
-      <c r="B198" s="2"/>
-      <c r="C198" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C198" s="3"/>
       <c r="D198" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" ht="30.5" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="G198" s="2"/>
+    </row>
+    <row r="199" ht="30.5" customHeight="1" spans="1:7">
       <c r="A199">
-        <v>199</v>
-      </c>
-      <c r="B199" s="2"/>
+        <v>194</v>
+      </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="200" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="G199" s="2"/>
+    </row>
+    <row r="200" ht="30.5" customHeight="1" spans="1:7">
       <c r="A200">
-        <v>200</v>
-      </c>
-      <c r="B200" s="2"/>
-      <c r="C200" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="D200" s="3" t="s">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="201" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="G200" s="2"/>
+    </row>
+    <row r="201" ht="30.5" customHeight="1" spans="1:7">
       <c r="A201">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B201" s="2"/>
-      <c r="C201" s="3" t="s">
+      <c r="C201" s="3"/>
+      <c r="D201" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D201" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="E201" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" ht="30.5" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" ht="30.5" customHeight="1" spans="1:7">
       <c r="A202">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B202" s="2"/>
       <c r="C202" s="3"/>
       <c r="D202" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203" ht="30.5" customHeight="1" spans="1:7">
+      <c r="A203">
+        <v>198</v>
+      </c>
+      <c r="B203" s="2"/>
+      <c r="C203" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D203" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E202" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="203" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A203">
-        <v>203</v>
-      </c>
-      <c r="B203" s="2"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="E203" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="204" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" ht="30.5" customHeight="1" spans="1:7">
       <c r="A204">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B204" s="2"/>
-      <c r="C204" s="3" t="s">
+      <c r="C204" s="3"/>
+      <c r="D204" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D204" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="E204" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" ht="30.5" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" ht="30.5" customHeight="1" spans="1:7">
       <c r="A205">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="206" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" ht="47" customHeight="1" spans="1:7">
       <c r="A206">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B206" s="2"/>
-      <c r="C206" s="3"/>
+      <c r="C206" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="D206" s="3" t="s">
-        <v>231</v>
+        <v>98</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="207" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" ht="30.5" customHeight="1" spans="1:7">
       <c r="A207">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B207" s="2"/>
-      <c r="C207" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="C207" s="3"/>
       <c r="D207" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" ht="30.5" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" ht="30.5" customHeight="1" spans="1:7">
       <c r="A208">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B208" s="2"/>
       <c r="C208" s="3"/>
       <c r="D208" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" ht="30.5" customHeight="1" spans="1:5">
       <c r="A209">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B209" s="2"/>
-      <c r="C209" s="3"/>
+      <c r="C209" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="D209" s="3" t="s">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" ht="30.5" customHeight="1" spans="1:5">
       <c r="A210">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B210" s="2"/>
-      <c r="C210" s="3" t="s">
+      <c r="C210" s="3"/>
+      <c r="D210" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D210" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="E210" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" ht="30.5" customHeight="1" spans="1:5">
       <c r="A211">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" ht="30.5" customHeight="1" spans="1:5">
       <c r="A212">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B212" s="2"/>
-      <c r="C212" s="3"/>
+      <c r="C212" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="D212" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="213" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" ht="30.5" customHeight="1" spans="1:5">
       <c r="A213">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B213" s="2"/>
-      <c r="C213" s="3" t="s">
+      <c r="C213" s="3"/>
+      <c r="D213" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D213" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="E213" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214" ht="30.5" customHeight="1" spans="1:5">
       <c r="A214">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B214" s="2"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3" t="s">
-        <v>227</v>
+        <v>158</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" ht="30.5" customHeight="1" spans="1:5">
       <c r="A215">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B215" s="2"/>
-      <c r="C215" s="3"/>
+      <c r="C215" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="D215" s="3" t="s">
-        <v>153</v>
+        <v>227</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" ht="30.5" customHeight="1" spans="1:5">
       <c r="A216">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B216" s="2"/>
-      <c r="C216" s="3" t="s">
-        <v>236</v>
-      </c>
+      <c r="C216" s="3"/>
       <c r="D216" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217" ht="30.5" customHeight="1" spans="1:5">
       <c r="A217">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="218" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218" ht="47" customHeight="1" spans="1:5">
       <c r="A218">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B218" s="2"/>
-      <c r="C218" s="3"/>
+      <c r="C218" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="D218" s="3" t="s">
-        <v>238</v>
+        <v>106</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" ht="30.5" customHeight="1" spans="1:5">
       <c r="A219">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B219" s="2"/>
-      <c r="C219" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="C219" s="3"/>
       <c r="D219" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="220" ht="30.5" customHeight="1" spans="1:5">
       <c r="A220">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B220" s="2"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="221" ht="30.5" customHeight="1" spans="1:5">
       <c r="A221">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B221" s="2"/>
-      <c r="C221" s="3"/>
+      <c r="C221" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="D221" s="3" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" ht="30.5" customHeight="1" spans="1:5">
       <c r="A222">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B222" s="2"/>
-      <c r="C222" s="3" t="s">
+      <c r="C222" s="3"/>
+      <c r="D222" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D222" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="E222" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" ht="30.5" customHeight="1" spans="1:5">
       <c r="A223">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B223" s="2"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" ht="30.5" customHeight="1" spans="1:5">
       <c r="A224">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B224" s="2"/>
-      <c r="C224" s="3"/>
+      <c r="C224" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="D224" s="3" t="s">
-        <v>242</v>
+        <v>98</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" ht="30.5" customHeight="1" spans="1:5">
       <c r="A225">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B225" s="2"/>
-      <c r="C225" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="C225" s="3"/>
       <c r="D225" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" ht="30.5" customHeight="1" spans="1:5">
       <c r="A226">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B226" s="2"/>
       <c r="C226" s="3"/>
       <c r="D226" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="227" ht="30.5" customHeight="1" spans="1:5">
       <c r="A227">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B227" s="2"/>
-      <c r="C227" s="3"/>
+      <c r="C227" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="D227" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" ht="30.5" customHeight="1" spans="1:5">
       <c r="A228">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B228" s="2"/>
-      <c r="C228" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="C228" s="3"/>
       <c r="D228" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229" ht="30.5" customHeight="1" spans="1:5">
       <c r="A229">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B229" s="2"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="230" ht="30.5" customHeight="1" spans="1:5">
       <c r="A230">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B230" s="2"/>
-      <c r="C230" s="3"/>
+      <c r="C230" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="D230" s="3" t="s">
-        <v>110</v>
+        <v>224</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="231" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" ht="30.5" customHeight="1" spans="1:5">
       <c r="A231">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B231" s="2"/>
-      <c r="C231" s="3" t="s">
-        <v>243</v>
-      </c>
+      <c r="C231" s="3"/>
       <c r="D231" s="3" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232" ht="30.5" customHeight="1" spans="1:5">
       <c r="A232">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B232" s="2"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3" t="s">
-        <v>244</v>
+        <v>158</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233" ht="30.5" customHeight="1" spans="1:5">
       <c r="A233">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B233" s="2"/>
-      <c r="C233" s="3"/>
+      <c r="C233" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="D233" s="3" t="s">
-        <v>153</v>
+        <v>243</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" ht="30.5" customHeight="1" spans="1:5">
       <c r="A234">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B234" s="2"/>
-      <c r="C234" s="3" t="s">
-        <v>245</v>
-      </c>
+      <c r="C234" s="3"/>
       <c r="D234" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="235" ht="30.5" customHeight="1" spans="1:5">
       <c r="A235">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B235" s="2"/>
-      <c r="C235" s="3"/>
+      <c r="C235" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="D235" s="3" t="s">
         <v>246</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="236" ht="47" customHeight="1" spans="1:5">
-      <c r="A236">
-        <v>236</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" ht="30.5" customHeight="1" spans="1:5">
       <c r="B236" s="2"/>
-      <c r="C236" s="3" t="s">
-        <v>247</v>
-      </c>
+      <c r="C236" s="3"/>
       <c r="D236" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" ht="30.5" customHeight="1" spans="1:5">
+        <v>147</v>
+      </c>
+      <c r="E236" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" ht="47" customHeight="1" spans="1:5">
       <c r="A237">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B237" s="2"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E237" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E237" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" ht="30.5" customHeight="1" spans="1:5">
       <c r="A238">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B238" s="2"/>
       <c r="C238" s="3"/>
       <c r="D238" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="239" ht="47" customHeight="1" spans="1:5">
+    <row r="239" ht="30.5" customHeight="1" spans="1:5">
       <c r="A239">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>1</v>
@@ -5237,12 +5242,12 @@
     </row>
     <row r="240" ht="30.5" customHeight="1" spans="1:5">
       <c r="A240">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B240" s="2"/>
       <c r="C240" s="3"/>
       <c r="D240" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>8</v>
@@ -5250,27 +5255,27 @@
     </row>
     <row r="241" ht="30.5" customHeight="1" spans="1:5">
       <c r="A241">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B241" s="2"/>
       <c r="C241" s="3"/>
       <c r="D241" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="242" ht="30.5" customHeight="1" spans="1:5">
+    <row r="242" ht="47" customHeight="1" spans="1:5">
       <c r="A242">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B242" s="2"/>
       <c r="C242" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>1</v>
@@ -5278,40 +5283,40 @@
     </row>
     <row r="243" ht="30.5" customHeight="1" spans="1:5">
       <c r="A243">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
       <c r="D243" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="244" ht="47" customHeight="1" spans="1:5">
+    <row r="244" ht="30.5" customHeight="1" spans="1:5">
       <c r="A244">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B244" s="2"/>
       <c r="C244" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="245" ht="30.5" customHeight="1" spans="1:5">
+    <row r="245" ht="47" customHeight="1" spans="1:5">
       <c r="A245">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B245" s="2"/>
       <c r="C245" s="3"/>
       <c r="D245" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>8</v>
@@ -5319,12 +5324,12 @@
     </row>
     <row r="246" ht="30.5" customHeight="1" spans="1:5">
       <c r="A246">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B246" s="2"/>
       <c r="C246" s="3"/>
       <c r="D246" s="3" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>12</v>
@@ -5332,14 +5337,14 @@
     </row>
     <row r="247" ht="30.5" customHeight="1" spans="1:5">
       <c r="A247">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B247" s="2"/>
       <c r="C247" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>1</v>
@@ -5347,53 +5352,53 @@
     </row>
     <row r="248" ht="30.5" customHeight="1" spans="1:5">
       <c r="A248">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B248" s="2"/>
       <c r="C248" s="3"/>
       <c r="D248" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="249" ht="47" customHeight="1" spans="1:5">
+    <row r="249" ht="30.5" customHeight="1" spans="1:5">
       <c r="A249">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B249" s="2"/>
       <c r="C249" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D249" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="E249" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="250" ht="30.5" customHeight="1" spans="1:5">
+    <row r="250" ht="47" customHeight="1" spans="1:5">
       <c r="A250">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B250" s="2"/>
       <c r="C250" s="3"/>
       <c r="D250" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="251" ht="47" customHeight="1" spans="1:5">
+    <row r="251" ht="30.5" customHeight="1" spans="1:5">
       <c r="A251">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B251" s="2"/>
       <c r="C251" s="3"/>
       <c r="D251" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>12</v>
@@ -5401,16 +5406,14 @@
     </row>
     <row r="252" ht="30.5" customHeight="1" spans="1:5">
       <c r="A252">
-        <v>252</v>
-      </c>
-      <c r="B252" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B252" s="2"/>
+      <c r="C252" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D252" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="C252" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>1</v>
@@ -5418,164 +5421,168 @@
     </row>
     <row r="253" ht="30.5" customHeight="1" spans="1:5">
       <c r="A253">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B253" s="2"/>
       <c r="C253" s="3"/>
       <c r="D253" s="3" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="254" ht="47" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" ht="30.5" customHeight="1" spans="1:5">
       <c r="A254">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B254" s="2"/>
-      <c r="C254" s="3" t="s">
-        <v>266</v>
-      </c>
+      <c r="C254" s="3"/>
       <c r="D254" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="255" ht="47" customHeight="1" spans="1:5">
       <c r="A255">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B255" s="2"/>
-      <c r="C255" s="3"/>
+      <c r="C255" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="D255" s="3" t="s">
-        <v>167</v>
+        <v>269</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="256" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" ht="30.5" customHeight="1" spans="1:5">
       <c r="A256">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
       <c r="D256" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="257" ht="30.5" customHeight="1" spans="1:10">
+    <row r="257" ht="47" customHeight="1" spans="1:10">
       <c r="A257">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B257" s="2"/>
       <c r="C257" s="3"/>
       <c r="D257" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="258" ht="30.5" customHeight="1" spans="1:10">
-      <c r="A258">
-        <v>258</v>
-      </c>
       <c r="B258" s="2"/>
       <c r="C258" s="3"/>
       <c r="D258" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="259" ht="47" customHeight="1" spans="1:10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" ht="30.5" customHeight="1" spans="1:10">
       <c r="A259">
-        <v>259</v>
-      </c>
-      <c r="B259" s="2"/>
-      <c r="C259" s="3"/>
+        <v>252</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="D259" s="3" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" ht="30.5" customHeight="1" spans="1:10">
       <c r="A260">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B260" s="2"/>
       <c r="C260" s="3"/>
       <c r="D260" s="3" t="s">
-        <v>271</v>
+        <v>206</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="261" ht="30.5" customHeight="1" spans="1:10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261" ht="47" customHeight="1" spans="1:10">
       <c r="A261">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B261" s="2"/>
+      <c r="C261" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="D261" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="262" ht="30.5" customHeight="1" spans="1:10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" ht="47" customHeight="1" spans="1:10">
+      <c r="A262">
+        <v>255</v>
+      </c>
       <c r="B262" s="2"/>
-      <c r="C262" s="3" t="s">
-        <v>273</v>
-      </c>
+      <c r="C262" s="3"/>
       <c r="D262" s="3" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="263" ht="30.5" customHeight="1" spans="1:10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" ht="47" customHeight="1" spans="1:10">
       <c r="A263">
-        <v>262</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="B263" s="2"/>
+      <c r="C263" s="3"/>
       <c r="D263" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" ht="30.5" customHeight="1" spans="1:10">
       <c r="A264">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B264" s="2"/>
-      <c r="C264" s="3" t="s">
-        <v>275</v>
-      </c>
+      <c r="C264" s="3"/>
       <c r="D264" s="3" t="s">
         <v>276</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J264" s="3"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="265" ht="30.5" customHeight="1" spans="1:10">
       <c r="A265">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B265" s="2"/>
       <c r="C265" s="3"/>
@@ -5586,94 +5593,91 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" ht="30.5" customHeight="1" spans="1:10">
+    <row r="266" ht="47" customHeight="1" spans="1:10">
       <c r="A266">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B266" s="2"/>
       <c r="C266" s="3"/>
       <c r="D266" s="3" t="s">
-        <v>207</v>
+        <v>278</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="267" ht="47" customHeight="1" spans="1:10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="267" ht="30.5" customHeight="1" spans="1:10">
       <c r="A267">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B267" s="2"/>
-      <c r="C267" s="3" t="s">
-        <v>278</v>
-      </c>
+      <c r="C267" s="3"/>
       <c r="D267" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268" ht="30.5" customHeight="1" spans="1:10">
       <c r="A268">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B268" s="2"/>
-      <c r="C268" s="3"/>
       <c r="D268" s="3" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="269" ht="30.5" customHeight="1" spans="1:10">
-      <c r="A269">
-        <v>268</v>
-      </c>
       <c r="B269" s="2"/>
-      <c r="C269" s="3"/>
+      <c r="C269" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="D269" s="3" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="270" ht="47" customHeight="1" spans="1:10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" ht="30.5" customHeight="1" spans="1:10">
       <c r="A270">
-        <v>269</v>
-      </c>
-      <c r="B270" s="2"/>
-      <c r="C270" s="3"/>
+        <v>262</v>
+      </c>
       <c r="D270" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271" ht="30.5" customHeight="1" spans="1:10">
       <c r="A271">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B271" s="2"/>
-      <c r="C271" s="3"/>
+      <c r="C271" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="D271" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J271" s="3"/>
     </row>
     <row r="272" ht="30.5" customHeight="1" spans="1:10">
       <c r="A272">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B272" s="2"/>
       <c r="C272" s="3"/>
       <c r="D272" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>8</v>
@@ -5681,228 +5685,337 @@
     </row>
     <row r="273" ht="30.5" customHeight="1" spans="1:5">
       <c r="A273">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B273" s="2"/>
       <c r="C273" s="3"/>
       <c r="D273" s="3" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="274" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274" ht="47" customHeight="1" spans="1:5">
       <c r="A274">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B274" s="2"/>
-      <c r="C274" s="3"/>
+      <c r="C274" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="D274" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" ht="30.5" customHeight="1" spans="1:5">
       <c r="A275">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B275" s="2"/>
-      <c r="C275" s="3" t="s">
-        <v>284</v>
-      </c>
+      <c r="C275" s="3"/>
       <c r="D275" s="3" t="s">
-        <v>284</v>
+        <v>147</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276" ht="30.5" customHeight="1" spans="1:5">
       <c r="A276">
+        <v>268</v>
+      </c>
+      <c r="B276" s="2"/>
+      <c r="C276" s="3"/>
+      <c r="D276" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B276" s="2"/>
-      <c r="D276" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="E276" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="277" ht="30.5" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="277" ht="47" customHeight="1" spans="1:5">
       <c r="A277">
+        <v>269</v>
+      </c>
+      <c r="B277" s="2"/>
+      <c r="C277" s="3"/>
+      <c r="D277" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B277" s="2"/>
-      <c r="C277" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E277" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" ht="30.5" customHeight="1" spans="1:5">
       <c r="A278">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B278" s="2"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3" t="s">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" ht="30.5" customHeight="1" spans="1:5">
       <c r="A279">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B279" s="2"/>
-      <c r="C279" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="C279" s="3"/>
       <c r="D279" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" ht="30.5" customHeight="1" spans="1:5">
       <c r="A280">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B280" s="2"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281" ht="30.5" customHeight="1" spans="1:5">
       <c r="A281">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B281" s="2"/>
-      <c r="C281" s="3" t="s">
-        <v>288</v>
-      </c>
+      <c r="C281" s="3"/>
       <c r="D281" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="282" ht="30.5" customHeight="1" spans="1:5">
       <c r="A282">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B282" s="2"/>
-      <c r="C282" s="3"/>
+      <c r="C282" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="D282" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" ht="30.5" customHeight="1" spans="1:5">
       <c r="A283">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B283" s="2"/>
-      <c r="C283" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="D283" s="3" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="284" ht="30.5" customHeight="1" spans="1:5">
       <c r="A284">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B284" s="2"/>
-      <c r="C284" s="3"/>
+      <c r="C284" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D284" s="3" t="s">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285" ht="30.5" customHeight="1" spans="1:5">
       <c r="A285">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B285" s="2"/>
-      <c r="C285" s="3" t="s">
-        <v>291</v>
-      </c>
+      <c r="C285" s="3"/>
       <c r="D285" s="3" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="286" ht="30.5" customHeight="1" spans="1:5">
       <c r="A286">
-        <v>285</v>
-      </c>
-      <c r="C286" s="3"/>
+        <v>278</v>
+      </c>
+      <c r="B286" s="2"/>
+      <c r="C286" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="D286" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287" ht="30.5" customHeight="1" spans="1:5">
       <c r="A287">
-        <v>286</v>
-      </c>
-      <c r="C287" s="3" t="s">
-        <v>293</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="B287" s="2"/>
+      <c r="C287" s="3"/>
       <c r="D287" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="288" ht="30.5" customHeight="1" spans="1:5">
       <c r="A288">
+        <v>280</v>
+      </c>
+      <c r="B288" s="2"/>
+      <c r="C288" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A289">
+        <v>281</v>
+      </c>
+      <c r="B289" s="2"/>
+      <c r="C289" s="3"/>
+      <c r="D289" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A290">
+        <v>282</v>
+      </c>
+      <c r="B290" s="2"/>
+      <c r="C290" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A291">
+        <v>283</v>
+      </c>
+      <c r="B291" s="2"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="292" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A292">
+        <v>284</v>
+      </c>
+      <c r="B292" s="2"/>
+      <c r="C292" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A293">
+        <v>285</v>
+      </c>
+      <c r="C293" s="3"/>
+      <c r="D293" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="294" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A294">
+        <v>286</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A295">
         <v>287</v>
       </c>
-      <c r="B288" s="2"/>
-      <c r="C288" s="3"/>
-      <c r="D288" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>12</v>
+      <c r="B295" s="2"/>
+      <c r="C295" s="3"/>
+      <c r="D295" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296" ht="16.5" spans="1:5">
+      <c r="D296" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="297" ht="16.5" spans="1:5">
+      <c r="D297" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C277:E287 B288:E288 B128:E139 E126:E127 B126:C127 B125:E125 B140 E140 B144:E144 E142:E143 B142:C143 B141:E141 B145 E145 B146:E147 B148:C148 E148 B149:E149 B92 B93:E99 B77 B78:E80 B83:B84 B163:E197 B199:B200 B201:E206 B207 E207 B208:E209 B210 E210 B211:E218 B219 E219 B220:E224 B225 E225 B226:E227 B228 E228 B229:E253 B264:E266 B267 E267 B268:E269 B270:C272 E270:E272 B273:E274 C162:E162 B150 D150:E150 B161:E161 E160 B160:C160 D159:E159 B159 B158:E158 E157 B157:C157 B155 E152:E155 B152:C154 B151:E151 C124:E124 B101:E114 B115:C115 E115 B116:E119 B120:C120 E120 B121:E123 C100:E100 B3:E22 B23:C23 E23 B24:E74 B75 B81 B86 B87:E89 B90 C2:E2 B1:E1" numberStoredAsText="1"/>
+    <ignoredError sqref="B237:B257 E127 B127:C127 D124:E124 B124 B123:E123 B99:E99 E96:E98 B97:C98 E101 B101:C101 B54 E54 B24:E53 B55:D55 B58:E63 E57 B57:C57 B129:E129 B105:E105 B110:E113 B115:E116 B120:E121 B161:C162 E161:E164 B163 C294 C284:E293 E294:E295 B295:C295 B132:E143 E130:E131 B130:C131 B144 E144 B148:E148 E146:E147 B146:C147 B145:E145 B149 E149 B150:E151 B152:C152 E152 B153:E153 B93 B96 B94:E95 B78 B79:E81 B84:B85 B168:E180 B181:C181 E181 B182:E187 B188:C188 E188 B189:E189 B190:C190 E190 B191:E194 B201:B202 B204:B235 B259:E260 B271:E273 B274 E274 B275:E276 B277:C279 E277:E279 E281 B281:C281 B280:E280 C167:E167 B154 D154:E154 B165:D165 B164:C164 B159 E156:E159 B156:C158 B155:E155 C128:E128 B103:E103 B104 E104 B106:C106 E106 B107:E108 B109 E109 B114 E114 B117:C117 E117 B118:E118 B119 E119 B122:C122 E122 C102:E102 B22:E22 E21 B21:C21 B3:E20 B23:C23 E23 B66:E75 E65 B65:C65 D64:E64 B64 B76 B82 B87 B88:E90 B91 C2:E2 B1:E1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>